--- a/hira_material_automation/output/monthly/202601_202608__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__arthroscopy_cannula__041001__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:16:47</t>
+          <t>2026-08-14T21:28:46</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>db7a0a1505e87951f7265eeea9b4565afc11d5cde70436d9ae99eea6409aae3f</t>
+          <t>644178f6e618653528fccb3eba0842d8e2a0e6955df1a27c896eecc246e22f9e</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__arthroscopy_cannula__041001__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:28:46</t>
+          <t>2026-08-24T21:33:56</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>644178f6e618653528fccb3eba0842d8e2a0e6955df1a27c896eecc246e22f9e</t>
+          <t>28a5336c5e947d5957245b88f0e648fe7f2a481a1853026691d7b66592b28830</t>
         </is>
       </c>
     </row>
